--- a/real_estate_prospects.xlsx
+++ b/real_estate_prospects.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2006"/>
+  <dimension ref="A1:I2029"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70650,6 +70650,811 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2007">
+      <c r="A2007" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B2007" t="n">
+        <v>20</v>
+      </c>
+      <c r="C2007" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D2007" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="E2007" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2007" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G2007" t="inlineStr">
+        <is>
+          <t>Marrakech</t>
+        </is>
+      </c>
+      <c r="H2007" t="inlineStr">
+        <is>
+          <t>villa</t>
+        </is>
+      </c>
+      <c r="I2007" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B2008" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2008" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2008" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E2008" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2008" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2008" t="inlineStr">
+        <is>
+          <t>Rabat</t>
+        </is>
+      </c>
+      <c r="H2008" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2008" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B2009" t="n">
+        <v>23</v>
+      </c>
+      <c r="C2009" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D2009" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="E2009" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2009" t="n">
+        <v>5620</v>
+      </c>
+      <c r="G2009" t="inlineStr">
+        <is>
+          <t>Marrakech</t>
+        </is>
+      </c>
+      <c r="H2009" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2009" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B2010" t="n">
+        <v>23</v>
+      </c>
+      <c r="C2010" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D2010" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2010" t="n">
+        <v>5620</v>
+      </c>
+      <c r="G2010" t="inlineStr">
+        <is>
+          <t>Marrakech</t>
+        </is>
+      </c>
+      <c r="H2010" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2010" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B2011" t="n">
+        <v>23</v>
+      </c>
+      <c r="C2011" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D2011" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E2011" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2011" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G2011" t="inlineStr">
+        <is>
+          <t>Marrakech</t>
+        </is>
+      </c>
+      <c r="H2011" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2011" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B2012" t="n">
+        <v>23</v>
+      </c>
+      <c r="C2012" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D2012" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E2012" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2012" t="n">
+        <v>60000</v>
+      </c>
+      <c r="G2012" t="inlineStr">
+        <is>
+          <t>Marrakech</t>
+        </is>
+      </c>
+      <c r="H2012" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2012" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B2013" t="n">
+        <v>23</v>
+      </c>
+      <c r="C2013" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D2013" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2013" t="n">
+        <v>60000</v>
+      </c>
+      <c r="G2013" t="inlineStr">
+        <is>
+          <t>Marrakech</t>
+        </is>
+      </c>
+      <c r="H2013" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2013" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B2014" t="n">
+        <v>23</v>
+      </c>
+      <c r="C2014" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D2014" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E2014" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2014" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G2014" t="inlineStr">
+        <is>
+          <t>Marrakech</t>
+        </is>
+      </c>
+      <c r="H2014" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2014" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B2015" t="n">
+        <v>23</v>
+      </c>
+      <c r="C2015" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D2015" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="E2015" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2015" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G2015" t="inlineStr">
+        <is>
+          <t>Marrakech</t>
+        </is>
+      </c>
+      <c r="H2015" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2015" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B2016" t="n">
+        <v>23</v>
+      </c>
+      <c r="C2016" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D2016" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="E2016" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2016" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G2016" t="inlineStr">
+        <is>
+          <t>Marrakech</t>
+        </is>
+      </c>
+      <c r="H2016" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2016" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B2017" t="n">
+        <v>23</v>
+      </c>
+      <c r="C2017" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D2017" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="E2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2017" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G2017" t="inlineStr">
+        <is>
+          <t>Marrakech</t>
+        </is>
+      </c>
+      <c r="H2017" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2017" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B2018" t="n">
+        <v>23</v>
+      </c>
+      <c r="C2018" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D2018" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="E2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2018" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G2018" t="inlineStr">
+        <is>
+          <t>Marrakech</t>
+        </is>
+      </c>
+      <c r="H2018" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2018" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B2019" t="n">
+        <v>23</v>
+      </c>
+      <c r="C2019" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D2019" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="E2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2019" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G2019" t="inlineStr">
+        <is>
+          <t>Marrakech</t>
+        </is>
+      </c>
+      <c r="H2019" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2019" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B2020" t="n">
+        <v>23</v>
+      </c>
+      <c r="C2020" t="n">
+        <v>100526</v>
+      </c>
+      <c r="D2020" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="E2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2020" t="n">
+        <v>449602</v>
+      </c>
+      <c r="G2020" t="inlineStr">
+        <is>
+          <t>Marrakech</t>
+        </is>
+      </c>
+      <c r="H2020" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2020" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B2021" t="n">
+        <v>64</v>
+      </c>
+      <c r="C2021" t="n">
+        <v>100526</v>
+      </c>
+      <c r="D2021" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="E2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2021" t="n">
+        <v>449602</v>
+      </c>
+      <c r="G2021" t="inlineStr">
+        <is>
+          <t>Marrakech</t>
+        </is>
+      </c>
+      <c r="H2021" t="inlineStr">
+        <is>
+          <t>villa</t>
+        </is>
+      </c>
+      <c r="I2021" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B2022" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2022" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2022" t="inlineStr">
+        <is>
+          <t>Rabat</t>
+        </is>
+      </c>
+      <c r="H2022" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2022" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B2023" t="n">
+        <v>45</v>
+      </c>
+      <c r="C2023" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D2023" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="E2023" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2023" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G2023" t="inlineStr">
+        <is>
+          <t>Rabat</t>
+        </is>
+      </c>
+      <c r="H2023" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2023" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B2024" t="n">
+        <v>45</v>
+      </c>
+      <c r="C2024" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D2024" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="E2024" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2024" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G2024" t="inlineStr">
+        <is>
+          <t>Rabat</t>
+        </is>
+      </c>
+      <c r="H2024" t="inlineStr">
+        <is>
+          <t>villa</t>
+        </is>
+      </c>
+      <c r="I2024" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B2025" t="n">
+        <v>62</v>
+      </c>
+      <c r="C2025" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D2025" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2025" t="n">
+        <v>105000</v>
+      </c>
+      <c r="G2025" t="inlineStr">
+        <is>
+          <t>Marrakech</t>
+        </is>
+      </c>
+      <c r="H2025" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2025" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B2026" t="n">
+        <v>62</v>
+      </c>
+      <c r="C2026" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D2026" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2026" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G2026" t="inlineStr">
+        <is>
+          <t>Marrakech</t>
+        </is>
+      </c>
+      <c r="H2026" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2026" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B2027" t="n">
+        <v>49</v>
+      </c>
+      <c r="C2027" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D2027" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2027" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G2027" t="inlineStr">
+        <is>
+          <t>Marrakech</t>
+        </is>
+      </c>
+      <c r="H2027" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2027" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B2028" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2028" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2028" t="inlineStr">
+        <is>
+          <t>Rabat</t>
+        </is>
+      </c>
+      <c r="H2028" t="inlineStr">
+        <is>
+          <t>apartment</t>
+        </is>
+      </c>
+      <c r="I2028" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B2029" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2029" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D2029" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="E2029" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2029" t="n">
+        <v>35000</v>
+      </c>
+      <c r="G2029" t="inlineStr">
+        <is>
+          <t>Casablanca</t>
+        </is>
+      </c>
+      <c r="H2029" t="inlineStr">
+        <is>
+          <t>villa</t>
+        </is>
+      </c>
+      <c r="I2029" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
